--- a/data/insurance-taxonomy.xlsx
+++ b/data/insurance-taxonomy.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="I3" s="32" t="inlineStr">
         <is>
-          <t>The most common individual life product sold in the US by policy count.</t>
+          <t>One of the most widely bought individual life products and the cheapest per dollar of cover; whole life and indexed UL now bring in more new premium.</t>
         </is>
       </c>
       <c r="J3" s="32" t="inlineStr">
